--- a/data/daily/2026-09/2026-09-07.xlsx
+++ b/data/daily/2026-09/2026-09-07.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,77 +1425,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,154 +1578,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2739,27 +2739,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43,000원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11866425</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
@@ -2774,27 +2774,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>43,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/11866425</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260831093017_c95c591e7b5b4e3d9e549888b299930a.jpg</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>39,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,34 +3159,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3194,27 +3194,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 10입 - 추석 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
           <t>43,000원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>64,200원</t>
+          <t>39,900원</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,34 +4062,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 마그네슘 30정 30일분</t>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157094&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/o7EiJdX7BYMCuTvEmVmE919157094_00_01o7EiJdX7BYMCuTvEmVmE.jpg</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,34 +4132,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>휴럼</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157095&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260826/gxSEg0bfLulOAScPenvi919157095_00_01gxSEg0bfLulOAScPenvi.jpg</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>판티오</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=033991022&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235549&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/bpRaPOFB6GapUUiby4Vv033991022_00_00bpRaPOFB6GapUUiby4Vv.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/kQh0cYBVEEUhZLYsuKrQ968235549_00_00kQh0cYBVEEUhZLYsuKrQ.jpg</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4212,24 +4212,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4322,19 +4322,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/XgyvZV5zt5ig9XLyfDOS613602129_00_01XgyvZV5zt5ig9XLyfDOS.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
         </is>
       </c>
     </row>
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>휴럼</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>판티오</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>휴럼 하루한알 침향환 9환 9일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>휴럼 하루한알 6년근 고려 홍삼환 9환 9일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[보령약국 X Pantio] 스트레스 케어 올인원 15포 15일분</t>
+          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 글루타치온 30정 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>오브맘 면역＆프로폴리스 하루구미 30일분</t>
         </is>
       </c>
     </row>
@@ -4683,37 +4683,37 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -4867,7 +4867,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549619ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[국민영양] 여에스더 마그네슘 30정 (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>에스더포뮬러</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9,700원</t>
+          <t>33,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227381&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022738113ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549619ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
+          <t>올더뮤 뮤신 딥글로우 자두맛 7포 (+2포 증정)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>올더뮤</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>16,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000171584&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236997&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017158410ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023699727ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000171584&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017158410ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 트루바이타민 포커스 3/4박스 (3/4개월분) +증정: 트루바이타민 12포</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5060,24 +5060,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>88,000원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000176865&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/B00000017686536ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,27 +5085,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>닥터아돌 프로폴리스아연C 120캡슐 (60일분)</t>
+          <t>[덴프스X카카오프렌즈] 덴마크 유산균이야기 30캡슐 1+1 기획 / 유산균이야기 우먼 기획 택 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>41,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218091&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021809120ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686145ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,27 +5155,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>14,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245840&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024584012ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -5325,14 +5325,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -5340,32 +5340,32 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>에스더포뮬러</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
@@ -5397,14 +5397,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>올더뮤</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5439,14 +5439,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[국민영양] 여에스더 마그네슘 30정 (1개월분)</t>
-        </is>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
@@ -5454,22 +5454,22 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>올더뮤 뮤신 딥글로우 자두맛 7포 (+2포 증정)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 트루바이타민 포커스 3/4박스 (3/4개월분) +증정: 트루바이타민 12포</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>닥터아돌 프로폴리스아연C 120캡슐 (60일분)</t>
+          <t>[덴프스X카카오프렌즈] 덴마크 유산균이야기 30캡슐 1+1 기획 / 유산균이야기 우먼 기획 택 1</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[1+1]알디콤 숙취해소제 4포입 3종 (플러스, 에이, 브이)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -5496,14 +5496,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>42,900원</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
           <t>33,900원</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>9,700원</t>
-        </is>
-      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>15,900원</t>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t>16,800원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
           <t>55,900원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>24,700원</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>88,000원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>41,400원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>14,800원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,45 +5667,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5715,16 +5715,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -5733,29 +5733,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5768,16 +5768,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5787,19 +5787,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,10 +5831,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5853,56 +5853,12 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
         <v>0</v>
       </c>
     </row>
